--- a/MAJEntreesCDA/ig/StructureDefinition-fr-cda-document-attache.xlsx
+++ b/MAJEntreesCDA/ig/StructureDefinition-fr-cda-document-attache.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T09:38:07+00:00</t>
+    <t>2026-04-20T13:30:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3646,7 +3646,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
         <v>137</v>
       </c>
@@ -3665,7 +3665,7 @@
         <v>75</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>74</v>
+        <v>131</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>74</v>
@@ -4050,7 +4050,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
         <v>146</v>
       </c>
@@ -4065,13 +4065,13 @@
         <v>62</v>
       </c>
       <c r="F23" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>74</v>
+        <v>131</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>74</v>
@@ -4153,7 +4153,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
         <v>150</v>
       </c>
@@ -4168,13 +4168,13 @@
         <v>151</v>
       </c>
       <c r="F24" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>74</v>
+        <v>131</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>74</v>
@@ -4462,7 +4462,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
         <v>164</v>
       </c>
@@ -4477,13 +4477,13 @@
         <v>165</v>
       </c>
       <c r="F27" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>74</v>
+        <v>131</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>74</v>
